--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/195.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/195.xlsx
@@ -426,13 +426,13 @@
         <v>-2.217255426241544</v>
       </c>
       <c r="E2">
-        <v>-15.01488673345391</v>
+        <v>-16.33745473823808</v>
       </c>
       <c r="F2">
-        <v>-2.658851590015818</v>
+        <v>-3.198369764561344</v>
       </c>
       <c r="G2">
-        <v>-8.905408377854299</v>
+        <v>-8.541685360545651</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-2.164209917494107</v>
       </c>
       <c r="E3">
-        <v>-16.31142506964199</v>
+        <v>-16.83640653287721</v>
       </c>
       <c r="F3">
-        <v>-2.664930978384964</v>
+        <v>-3.592505318078544</v>
       </c>
       <c r="G3">
-        <v>-7.866565808722078</v>
+        <v>-8.823988820861462</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-2.140221122961912</v>
       </c>
       <c r="E4">
-        <v>-16.88597973783918</v>
+        <v>-16.66611326781877</v>
       </c>
       <c r="F4">
-        <v>-2.850368476808258</v>
+        <v>-3.308385239327147</v>
       </c>
       <c r="G4">
-        <v>-8.962214028762652</v>
+        <v>-8.33169745698968</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-2.145188067326512</v>
       </c>
       <c r="E5">
-        <v>-17.61291755639447</v>
+        <v>-18.00945791135013</v>
       </c>
       <c r="F5">
-        <v>-3.021997090626885</v>
+        <v>-3.329713214847026</v>
       </c>
       <c r="G5">
-        <v>-8.736487791712985</v>
+        <v>-8.387645676603363</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-2.166652265356593</v>
       </c>
       <c r="E6">
-        <v>-17.28429072613184</v>
+        <v>-19.35325993075627</v>
       </c>
       <c r="F6">
-        <v>-3.513971946456137</v>
+        <v>-3.188706030440286</v>
       </c>
       <c r="G6">
-        <v>-8.734061161832701</v>
+        <v>-7.997961361175752</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-2.187190364879278</v>
       </c>
       <c r="E7">
-        <v>-18.26517178161526</v>
+        <v>-19.20658265764783</v>
       </c>
       <c r="F7">
-        <v>-3.235973502811428</v>
+        <v>-3.275768272841916</v>
       </c>
       <c r="G7">
-        <v>-8.640971931813933</v>
+        <v>-8.025091281870079</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-2.187430211506228</v>
       </c>
       <c r="E8">
-        <v>-20.83750351456229</v>
+        <v>-18.80065930454827</v>
       </c>
       <c r="F8">
-        <v>-3.099506600139432</v>
+        <v>-3.468846632188634</v>
       </c>
       <c r="G8">
-        <v>-8.721881664793722</v>
+        <v>-7.7809782748953</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-2.146828291763076</v>
       </c>
       <c r="E9">
-        <v>-19.57635520274415</v>
+        <v>-20.45309041299917</v>
       </c>
       <c r="F9">
-        <v>-3.216278239442467</v>
+        <v>-3.300315284089074</v>
       </c>
       <c r="G9">
-        <v>-8.329727682393814</v>
+        <v>-7.960148310026196</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-2.046445523260515</v>
       </c>
       <c r="E10">
-        <v>-20.28127105220014</v>
+        <v>-20.19001324399757</v>
       </c>
       <c r="F10">
-        <v>-2.970164485498914</v>
+        <v>-3.221578134085578</v>
       </c>
       <c r="G10">
-        <v>-7.794601169789401</v>
+        <v>-6.897300975188721</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-1.873227586779004</v>
       </c>
       <c r="E11">
-        <v>-20.97600236361288</v>
+        <v>-21.01760545432135</v>
       </c>
       <c r="F11">
-        <v>-3.076116818153985</v>
+        <v>-3.373436103101589</v>
       </c>
       <c r="G11">
-        <v>-6.703352664770518</v>
+        <v>-7.454455857811443</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-1.620150017537618</v>
       </c>
       <c r="E12">
-        <v>-19.85722021764788</v>
+        <v>-22.37146974297253</v>
       </c>
       <c r="F12">
-        <v>-3.527138017956232</v>
+        <v>-3.209245400192699</v>
       </c>
       <c r="G12">
-        <v>-6.098539168564447</v>
+        <v>-7.262818308179653</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-1.287416696616483</v>
       </c>
       <c r="E13">
-        <v>-23.27643093171736</v>
+        <v>-22.02844236536551</v>
       </c>
       <c r="F13">
-        <v>-2.824498562818829</v>
+        <v>-3.122377824130726</v>
       </c>
       <c r="G13">
-        <v>-6.095615956853271</v>
+        <v>-6.141145889654868</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-0.8816366248783601</v>
       </c>
       <c r="E14">
-        <v>-22.07271272726449</v>
+        <v>-21.9046927561579</v>
       </c>
       <c r="F14">
-        <v>-2.976972008815121</v>
+        <v>-2.669441438893207</v>
       </c>
       <c r="G14">
-        <v>-5.375443190785756</v>
+        <v>-6.345072184328433</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-0.4146662358525743</v>
       </c>
       <c r="E15">
-        <v>-25.08287091269512</v>
+        <v>-23.04731731777329</v>
       </c>
       <c r="F15">
-        <v>-2.635005377591429</v>
+        <v>-2.777522675773473</v>
       </c>
       <c r="G15">
-        <v>-5.498741148850373</v>
+        <v>-5.21621588198343</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>0.09785439845725656</v>
       </c>
       <c r="E16">
-        <v>-22.82151401832882</v>
+        <v>-24.56804681665911</v>
       </c>
       <c r="F16">
-        <v>-2.411779414987226</v>
+        <v>-2.55433813153941</v>
       </c>
       <c r="G16">
-        <v>-5.099836964095891</v>
+        <v>-4.944797495400742</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>0.6375096230268835</v>
       </c>
       <c r="E17">
-        <v>-25.17150220597324</v>
+        <v>-25.07106065248312</v>
       </c>
       <c r="F17">
-        <v>-2.3705532260847</v>
+        <v>-2.780200787586723</v>
       </c>
       <c r="G17">
-        <v>-4.947005629275436</v>
+        <v>-4.676613511809923</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>1.182265553839057</v>
       </c>
       <c r="E18">
-        <v>-26.26989263348171</v>
+        <v>-25.97767020576674</v>
       </c>
       <c r="F18">
-        <v>-1.643642606045273</v>
+        <v>-2.727604427713371</v>
       </c>
       <c r="G18">
-        <v>-4.815855057191669</v>
+        <v>-4.653638325767381</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>1.709667864711551</v>
       </c>
       <c r="E19">
-        <v>-26.10785930501325</v>
+        <v>-26.37805976362892</v>
       </c>
       <c r="F19">
-        <v>-2.212787340751924</v>
+        <v>-2.156756569626565</v>
       </c>
       <c r="G19">
-        <v>-4.791327225291209</v>
+        <v>-5.084181394240677</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>2.197386572649389</v>
       </c>
       <c r="E20">
-        <v>-26.22698081378502</v>
+        <v>-26.57755715756283</v>
       </c>
       <c r="F20">
-        <v>-1.692999221006276</v>
+        <v>-1.709277468838689</v>
       </c>
       <c r="G20">
-        <v>-4.079996926359088</v>
+        <v>-3.819281533504864</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>2.624320885083138</v>
       </c>
       <c r="E21">
-        <v>-26.76353252810983</v>
+        <v>-27.30524670280339</v>
       </c>
       <c r="F21">
-        <v>-1.152913614789832</v>
+        <v>-1.875883691094142</v>
       </c>
       <c r="G21">
-        <v>-3.750246727374441</v>
+        <v>-4.457081305464232</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>2.970088310398704</v>
       </c>
       <c r="E22">
-        <v>-27.62097191061817</v>
+        <v>-27.73100477205655</v>
       </c>
       <c r="F22">
-        <v>-1.259425923809195</v>
+        <v>-1.669248270833208</v>
       </c>
       <c r="G22">
-        <v>-4.372692189122671</v>
+        <v>-4.991201412224707</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>3.214802074158014</v>
       </c>
       <c r="E23">
-        <v>-27.63335728702915</v>
+        <v>-27.79263277482693</v>
       </c>
       <c r="F23">
-        <v>-1.416286403570712</v>
+        <v>-1.810631534040819</v>
       </c>
       <c r="G23">
-        <v>-4.326169092659293</v>
+        <v>-4.063543515028909</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>3.342267078660392</v>
       </c>
       <c r="E24">
-        <v>-26.37641592756414</v>
+        <v>-27.14237560664352</v>
       </c>
       <c r="F24">
-        <v>-0.992435654580289</v>
+        <v>-1.565701517115867</v>
       </c>
       <c r="G24">
-        <v>-3.336163691322402</v>
+        <v>-4.21316693122181</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>3.33826239861579</v>
       </c>
       <c r="E25">
-        <v>-28.22620246174332</v>
+        <v>-27.43507805260331</v>
       </c>
       <c r="F25">
-        <v>-1.168073566628465</v>
+        <v>-1.278933976145123</v>
       </c>
       <c r="G25">
-        <v>-4.151594094736906</v>
+        <v>-3.72563282128996</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>3.196236402972786</v>
       </c>
       <c r="E26">
-        <v>-28.85478635332602</v>
+        <v>-28.35230687743491</v>
       </c>
       <c r="F26">
-        <v>-1.097349214512249</v>
+        <v>-1.140049069024355</v>
       </c>
       <c r="G26">
-        <v>-3.6986518751449</v>
+        <v>-4.708262327165356</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>2.91814004326256</v>
       </c>
       <c r="E27">
-        <v>-29.0810741994893</v>
+        <v>-28.6140753174483</v>
       </c>
       <c r="F27">
-        <v>-1.086547303579744</v>
+        <v>-1.317391761187493</v>
       </c>
       <c r="G27">
-        <v>-4.064271835047549</v>
+        <v>-4.398527686511144</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.512466663868145</v>
       </c>
       <c r="E28">
-        <v>-27.49774307592145</v>
+        <v>-27.83933492726804</v>
       </c>
       <c r="F28">
-        <v>-1.175952168996492</v>
+        <v>-1.390392466926602</v>
       </c>
       <c r="G28">
-        <v>-4.528877106574407</v>
+        <v>-4.367130472616696</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.997877553739095</v>
       </c>
       <c r="E29">
-        <v>-28.37319219955829</v>
+        <v>-27.80125951781154</v>
       </c>
       <c r="F29">
-        <v>-1.356524665663144</v>
+        <v>-1.250596355662755</v>
       </c>
       <c r="G29">
-        <v>-3.932005609117048</v>
+        <v>-4.596842606495644</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>1.399765083641603</v>
       </c>
       <c r="E30">
-        <v>-30.26612603408255</v>
+        <v>-26.71353817506516</v>
       </c>
       <c r="F30">
-        <v>-0.9186861047090491</v>
+        <v>-1.211382271181629</v>
       </c>
       <c r="G30">
-        <v>-5.531161321316455</v>
+        <v>-5.07076706371555</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>0.7488776410132132</v>
       </c>
       <c r="E31">
-        <v>-28.88196625432005</v>
+        <v>-26.89873464808284</v>
       </c>
       <c r="F31">
-        <v>-0.8440767094737032</v>
+        <v>-1.234648626424059</v>
       </c>
       <c r="G31">
-        <v>-4.074408725488798</v>
+        <v>-4.534531518355482</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.07969084471450144</v>
       </c>
       <c r="E32">
-        <v>-28.4638839485099</v>
+        <v>-27.59538150400083</v>
       </c>
       <c r="F32">
-        <v>-1.570404987228963</v>
+        <v>-1.409267646566792</v>
       </c>
       <c r="G32">
-        <v>-3.782461646017089</v>
+        <v>-5.222443018142799</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.5734318740630604</v>
       </c>
       <c r="E33">
-        <v>-27.52666643940844</v>
+        <v>-26.9786486288962</v>
       </c>
       <c r="F33">
-        <v>-0.6624273351834108</v>
+        <v>-1.916087674621613</v>
       </c>
       <c r="G33">
-        <v>-3.508275643363571</v>
+        <v>-4.760926485604082</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.177280310805513</v>
       </c>
       <c r="E34">
-        <v>-26.80087432477709</v>
+        <v>-25.61123514601407</v>
       </c>
       <c r="F34">
-        <v>-1.413246295202438</v>
+        <v>-1.334918358695925</v>
       </c>
       <c r="G34">
-        <v>-4.63147422338196</v>
+        <v>-5.222260938138139</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.703857065081326</v>
       </c>
       <c r="E35">
-        <v>-26.70638771460704</v>
+        <v>-25.55217478800603</v>
       </c>
       <c r="F35">
-        <v>-0.9041466000551122</v>
+        <v>-1.425566603584275</v>
       </c>
       <c r="G35">
-        <v>-5.133578044232142</v>
+        <v>-4.804069515071864</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.130865194680896</v>
       </c>
       <c r="E36">
-        <v>-24.39871358809029</v>
+        <v>-25.87200279327176</v>
       </c>
       <c r="F36">
-        <v>-1.045753522461479</v>
+        <v>-1.072651440397782</v>
       </c>
       <c r="G36">
-        <v>-4.972172396464976</v>
+        <v>-6.003668865045553</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.443477403112681</v>
       </c>
       <c r="E37">
-        <v>-25.71105177009114</v>
+        <v>-24.74163228232113</v>
       </c>
       <c r="F37">
-        <v>-0.8907941458893869</v>
+        <v>-1.303040295933992</v>
       </c>
       <c r="G37">
-        <v>-4.979879346480399</v>
+        <v>-5.903485135936128</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.636307102296657</v>
       </c>
       <c r="E38">
-        <v>-24.32156650489562</v>
+        <v>-25.09104027980496</v>
       </c>
       <c r="F38">
-        <v>-0.4454182699372187</v>
+        <v>-1.118407142258816</v>
       </c>
       <c r="G38">
-        <v>-6.1110199252475</v>
+        <v>-5.844266097329646</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.710228395401725</v>
       </c>
       <c r="E39">
-        <v>-24.09320008916281</v>
+        <v>-24.07868632996823</v>
       </c>
       <c r="F39">
-        <v>-1.142511805312878</v>
+        <v>-1.140830219485195</v>
       </c>
       <c r="G39">
-        <v>-5.434562913026062</v>
+        <v>-6.033576333447329</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.674805408481023</v>
       </c>
       <c r="E40">
-        <v>-24.77284252518199</v>
+        <v>-23.06492402471511</v>
       </c>
       <c r="F40">
-        <v>-1.471096989511747</v>
+        <v>-1.460500513695136</v>
       </c>
       <c r="G40">
-        <v>-5.222138447953186</v>
+        <v>-6.291024217854292</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.546389770200195</v>
       </c>
       <c r="E41">
-        <v>-21.87137677288347</v>
+        <v>-22.47886250406443</v>
       </c>
       <c r="F41">
-        <v>-1.025257227814011</v>
+        <v>-1.326132694021833</v>
       </c>
       <c r="G41">
-        <v>-6.203900590897292</v>
+        <v>-5.939073500483294</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.34572151094224</v>
       </c>
       <c r="E42">
-        <v>-22.39822396740985</v>
+        <v>-22.93070005512776</v>
       </c>
       <c r="F42">
-        <v>-1.410141574176745</v>
+        <v>-1.256690654645151</v>
       </c>
       <c r="G42">
-        <v>-5.259153657627778</v>
+        <v>-5.505147054468862</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.098014329431669</v>
       </c>
       <c r="E43">
-        <v>-22.34712013823329</v>
+        <v>-21.89247493328521</v>
       </c>
       <c r="F43">
-        <v>-1.831830284245862</v>
+        <v>-1.326672789568459</v>
       </c>
       <c r="G43">
-        <v>-5.994554933175939</v>
+        <v>-6.528804151212445</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.829341963228188</v>
       </c>
       <c r="E44">
-        <v>-22.44436006059999</v>
+        <v>-21.0298549765121</v>
       </c>
       <c r="F44">
-        <v>-1.038429097885926</v>
+        <v>-1.247203362780888</v>
       </c>
       <c r="G44">
-        <v>-5.924176045556574</v>
+        <v>-5.957884020237432</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.567783540563358</v>
       </c>
       <c r="E45">
-        <v>-21.45454885437345</v>
+        <v>-20.8850932479089</v>
       </c>
       <c r="F45">
-        <v>-0.3596408253773299</v>
+        <v>-0.9670064320491498</v>
       </c>
       <c r="G45">
-        <v>-5.004165508556492</v>
+        <v>-6.208171194642953</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.336146894561779</v>
       </c>
       <c r="E46">
-        <v>-21.35679268596987</v>
+        <v>-19.74797531068684</v>
       </c>
       <c r="F46">
-        <v>-0.5509290827665974</v>
+        <v>-1.291400905557256</v>
       </c>
       <c r="G46">
-        <v>-5.360817200593256</v>
+        <v>-5.653141682256441</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.154608625218895</v>
       </c>
       <c r="E47">
-        <v>-19.73550389326972</v>
+        <v>-19.13900876850537</v>
       </c>
       <c r="F47">
-        <v>-0.5917502000091542</v>
+        <v>-1.060606149993674</v>
       </c>
       <c r="G47">
-        <v>-4.843713297904636</v>
+        <v>-6.33432284296242</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.040246512565439</v>
       </c>
       <c r="E48">
-        <v>-19.53987834461237</v>
+        <v>-19.0588502500956</v>
       </c>
       <c r="F48">
-        <v>-0.5734581910205355</v>
+        <v>-1.135245366455521</v>
       </c>
       <c r="G48">
-        <v>-6.729426521437818</v>
+        <v>-6.998361998866052</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.998353754626178</v>
       </c>
       <c r="E49">
-        <v>-19.63888437184206</v>
+        <v>-17.95714497961352</v>
       </c>
       <c r="F49">
-        <v>-0.6492132183739531</v>
+        <v>-1.031750799884556</v>
       </c>
       <c r="G49">
-        <v>-5.198289277888277</v>
+        <v>-6.278851341906392</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.033622065677144</v>
       </c>
       <c r="E50">
-        <v>-16.18317868574477</v>
+        <v>-18.13443020853981</v>
       </c>
       <c r="F50">
-        <v>-0.4740458190105669</v>
+        <v>-1.210432133770618</v>
       </c>
       <c r="G50">
-        <v>-5.077921152625915</v>
+        <v>-6.826408953010768</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.143836748184687</v>
       </c>
       <c r="E51">
-        <v>-18.39288380557958</v>
+        <v>-17.47717654801455</v>
       </c>
       <c r="F51">
-        <v>-1.114466598523698</v>
+        <v>-1.522715047482393</v>
       </c>
       <c r="G51">
-        <v>-6.50097901595487</v>
+        <v>-7.212875418174208</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-1.315425926761853</v>
       </c>
       <c r="E52">
-        <v>-16.29359646747379</v>
+        <v>-17.56624710327142</v>
       </c>
       <c r="F52">
-        <v>-0.5468907916779497</v>
+        <v>-1.247282886051557</v>
       </c>
       <c r="G52">
-        <v>-6.468681333673741</v>
+        <v>-6.643838987611041</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.538288497616021</v>
       </c>
       <c r="E53">
-        <v>-17.20831651770515</v>
+        <v>-15.15874729572958</v>
       </c>
       <c r="F53">
-        <v>-0.7093560052868084</v>
+        <v>-1.164013737987345</v>
       </c>
       <c r="G53">
-        <v>-6.439402868924427</v>
+        <v>-6.425518440932724</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.796135625206147</v>
       </c>
       <c r="E54">
-        <v>-16.62600004505882</v>
+        <v>-16.31282889658437</v>
       </c>
       <c r="F54">
-        <v>-0.3827970077551873</v>
+        <v>-1.433700343112363</v>
       </c>
       <c r="G54">
-        <v>-6.211197033265846</v>
+        <v>-6.73736520964099</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.069094606321461</v>
       </c>
       <c r="E55">
-        <v>-15.72630547158491</v>
+        <v>-16.24876004632385</v>
       </c>
       <c r="F55">
-        <v>-0.6335305667041529</v>
+        <v>-1.551999491906161</v>
       </c>
       <c r="G55">
-        <v>-6.541794731908546</v>
+        <v>-8.127549355764984</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.346207223662609</v>
       </c>
       <c r="E56">
-        <v>-15.96024191034716</v>
+        <v>-15.1656079338512</v>
       </c>
       <c r="F56">
-        <v>-0.647225964974637</v>
+        <v>-1.497488774964939</v>
       </c>
       <c r="G56">
-        <v>-7.793372957394332</v>
+        <v>-7.700253932465712</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.614140004944415</v>
       </c>
       <c r="E57">
-        <v>-16.08076271758729</v>
+        <v>-15.0567434187068</v>
       </c>
       <c r="F57">
-        <v>-0.1953979353220635</v>
+        <v>-1.232362332392332</v>
       </c>
       <c r="G57">
-        <v>-7.942678561215462</v>
+        <v>-7.962644461362807</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.862024447651989</v>
       </c>
       <c r="E58">
-        <v>-13.9173567160069</v>
+        <v>-15.05743627522998</v>
       </c>
       <c r="F58">
-        <v>-0.8420182164777464</v>
+        <v>-1.097993684351627</v>
       </c>
       <c r="G58">
-        <v>-7.277745558016226</v>
+        <v>-7.346978996879005</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.086847483641366</v>
       </c>
       <c r="E59">
-        <v>-14.57489114192064</v>
+        <v>-14.2400603022675</v>
       </c>
       <c r="F59">
-        <v>-0.5616953739007825</v>
+        <v>-1.420508592222781</v>
       </c>
       <c r="G59">
-        <v>-7.806121868266065</v>
+        <v>-8.033288192625315</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.283162364128646</v>
       </c>
       <c r="E60">
-        <v>-14.50229970357768</v>
+        <v>-13.31795883940364</v>
       </c>
       <c r="F60">
-        <v>-0.5986471870048629</v>
+        <v>-1.129703588530792</v>
       </c>
       <c r="G60">
-        <v>-8.025101213506696</v>
+        <v>-8.36144932975111</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.449897285524838</v>
       </c>
       <c r="E61">
-        <v>-13.76448449045597</v>
+        <v>-13.25115026236848</v>
       </c>
       <c r="F61">
-        <v>-1.057978568591994</v>
+        <v>-1.251955706570749</v>
       </c>
       <c r="G61">
-        <v>-7.152345403534174</v>
+        <v>-8.507755579313661</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.589814643009932</v>
       </c>
       <c r="E62">
-        <v>-14.25881271313326</v>
+        <v>-12.10922761422428</v>
       </c>
       <c r="F62">
-        <v>-0.5598083529572052</v>
+        <v>-1.259850876286831</v>
       </c>
       <c r="G62">
-        <v>-7.61690763796902</v>
+        <v>-8.65302893866796</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.701021113144021</v>
       </c>
       <c r="E63">
-        <v>-13.79571737568687</v>
+        <v>-12.58306902049088</v>
       </c>
       <c r="F63">
-        <v>-1.012756335338364</v>
+        <v>-1.656323254247328</v>
       </c>
       <c r="G63">
-        <v>-7.132978712129437</v>
+        <v>-7.995008354554722</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.786029813288353</v>
       </c>
       <c r="E64">
-        <v>-14.03004326321377</v>
+        <v>-11.83659989354051</v>
       </c>
       <c r="F64">
-        <v>-0.663806566909072</v>
+        <v>-1.709633666821893</v>
       </c>
       <c r="G64">
-        <v>-7.333657361628978</v>
+        <v>-8.410130901906093</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.845926278729744</v>
       </c>
       <c r="E65">
-        <v>-12.92032712221213</v>
+        <v>-12.70726242015124</v>
       </c>
       <c r="F65">
-        <v>-1.499413072441643</v>
+        <v>-1.385451255368903</v>
       </c>
       <c r="G65">
-        <v>-8.590860203985986</v>
+        <v>-8.688951668314591</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.876486607220849</v>
       </c>
       <c r="E66">
-        <v>-13.45822379331722</v>
+        <v>-13.49152619116963</v>
       </c>
       <c r="F66">
-        <v>-1.404030707846293</v>
+        <v>-1.47467222322223</v>
       </c>
       <c r="G66">
-        <v>-7.731664388542317</v>
+        <v>-8.259901655879506</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.880398053358663</v>
       </c>
       <c r="E67">
-        <v>-12.88119657831185</v>
+        <v>-11.68128229202543</v>
       </c>
       <c r="F67">
-        <v>-1.361212396795587</v>
+        <v>-1.860485997810905</v>
       </c>
       <c r="G67">
-        <v>-8.063874322862642</v>
+        <v>-8.343701495115077</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.857712374703956</v>
       </c>
       <c r="E68">
-        <v>-12.76838323383276</v>
+        <v>-11.29859453905923</v>
       </c>
       <c r="F68">
-        <v>-1.464836188681388</v>
+        <v>-1.878388674120208</v>
       </c>
       <c r="G68">
-        <v>-8.093401078527402</v>
+        <v>-8.620393580741824</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.804760493442383</v>
       </c>
       <c r="E69">
-        <v>-13.44855097283684</v>
+        <v>-12.9223196507755</v>
       </c>
       <c r="F69">
-        <v>-1.542662134541805</v>
+        <v>-1.434426821324619</v>
       </c>
       <c r="G69">
-        <v>-6.986533419654236</v>
+        <v>-8.384609906343851</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.723868496829494</v>
       </c>
       <c r="E70">
-        <v>-12.32793479489873</v>
+        <v>-12.3717251385529</v>
       </c>
       <c r="F70">
-        <v>-1.37202838997394</v>
+        <v>-1.916622799963822</v>
       </c>
       <c r="G70">
-        <v>-8.396872167021312</v>
+        <v>-8.792091714590585</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.612781916729647</v>
       </c>
       <c r="E71">
-        <v>-13.81985867062176</v>
+        <v>-12.31468447995229</v>
       </c>
       <c r="F71">
-        <v>-1.491418498637225</v>
+        <v>-2.015663235009934</v>
       </c>
       <c r="G71">
-        <v>-9.155824663535849</v>
+        <v>-8.23349343411274</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.468515021193484</v>
       </c>
       <c r="E72">
-        <v>-13.5726855023351</v>
+        <v>-12.23235682249284</v>
       </c>
       <c r="F72">
-        <v>-1.589092127468717</v>
+        <v>-2.335268916562456</v>
       </c>
       <c r="G72">
-        <v>-7.476388222009115</v>
+        <v>-7.592465880252581</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.294307597328731</v>
       </c>
       <c r="E73">
-        <v>-13.24995474523045</v>
+        <v>-11.30721222509582</v>
       </c>
       <c r="F73">
-        <v>-1.730826618455115</v>
+        <v>-2.439856928105116</v>
       </c>
       <c r="G73">
-        <v>-6.622244299058375</v>
+        <v>-7.617894180539723</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.089464141865669</v>
       </c>
       <c r="E74">
-        <v>-13.1480233237918</v>
+        <v>-12.88721944874205</v>
       </c>
       <c r="F74">
-        <v>-1.650767394076751</v>
+        <v>-2.527517251771568</v>
       </c>
       <c r="G74">
-        <v>-7.67086953025914</v>
+        <v>-7.267681499576842</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.855748439594006</v>
       </c>
       <c r="E75">
-        <v>-14.76745997062281</v>
+        <v>-12.39128361779203</v>
       </c>
       <c r="F75">
-        <v>-1.783418836491453</v>
+        <v>-2.577735368831482</v>
       </c>
       <c r="G75">
-        <v>-6.767107150765803</v>
+        <v>-7.472600957912189</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.598429479454721</v>
       </c>
       <c r="E76">
-        <v>-14.81617276552332</v>
+        <v>-13.0849099815469</v>
       </c>
       <c r="F76">
-        <v>-1.336101267347123</v>
+        <v>-2.268982128623036</v>
       </c>
       <c r="G76">
-        <v>-7.399159815668997</v>
+        <v>-7.717948798373116</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.31967008310931</v>
       </c>
       <c r="E77">
-        <v>-14.76532253089119</v>
+        <v>-13.92431245208268</v>
       </c>
       <c r="F77">
-        <v>-2.045682441319985</v>
+        <v>-2.661548754279333</v>
       </c>
       <c r="G77">
-        <v>-5.680102765128265</v>
+        <v>-7.545290606317967</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.025667700668083</v>
       </c>
       <c r="E78">
-        <v>-14.77708297788911</v>
+        <v>-14.16916251320341</v>
       </c>
       <c r="F78">
-        <v>-1.971844256136645</v>
+        <v>-2.822850111687258</v>
       </c>
       <c r="G78">
-        <v>-6.137808859751282</v>
+        <v>-6.53732218488499</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-1.723680407162861</v>
       </c>
       <c r="E79">
-        <v>-16.03272013683992</v>
+        <v>-15.81567037765228</v>
       </c>
       <c r="F79">
-        <v>-2.874063097997935</v>
+        <v>-2.869247798285462</v>
       </c>
       <c r="G79">
-        <v>-5.668416539374639</v>
+        <v>-6.691302279007571</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-1.41881929857682</v>
       </c>
       <c r="E80">
-        <v>-15.54149844733189</v>
+        <v>-16.10822338396981</v>
       </c>
       <c r="F80">
-        <v>-2.229127716139546</v>
+        <v>-2.81034010717018</v>
       </c>
       <c r="G80">
-        <v>-5.02130089226776</v>
+        <v>-6.629428182878593</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-1.120685384239589</v>
       </c>
       <c r="E81">
-        <v>-16.91639296927469</v>
+        <v>-15.74491297128243</v>
       </c>
       <c r="F81">
-        <v>-2.380902020047875</v>
+        <v>-2.669660127887546</v>
       </c>
       <c r="G81">
-        <v>-6.423439418334061</v>
+        <v>-6.133157543268606</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-0.8376397811239354</v>
       </c>
       <c r="E82">
-        <v>-18.71924639883838</v>
+        <v>-16.67963981967968</v>
       </c>
       <c r="F82">
-        <v>-2.267840638341978</v>
+        <v>-2.641797990294385</v>
       </c>
       <c r="G82">
-        <v>-5.734021620326375</v>
+        <v>-5.814792310393514</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-0.5753544474758782</v>
       </c>
       <c r="E83">
-        <v>-18.70242311789988</v>
+        <v>-17.6306465321345</v>
       </c>
       <c r="F83">
-        <v>-2.441600641488009</v>
+        <v>-3.267144139811371</v>
       </c>
       <c r="G83">
-        <v>-5.549435532693232</v>
+        <v>-5.521309137791584</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-0.3429162011568548</v>
       </c>
       <c r="E84">
-        <v>-20.117652757829</v>
+        <v>-19.2246331550424</v>
       </c>
       <c r="F84">
-        <v>-2.556636022714776</v>
+        <v>-3.286123693744313</v>
       </c>
       <c r="G84">
-        <v>-5.254909538246432</v>
+        <v>-5.287429027078693</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-0.1451540372507042</v>
       </c>
       <c r="E85">
-        <v>-20.00052830609462</v>
+        <v>-19.88928181362219</v>
       </c>
       <c r="F85">
-        <v>-2.874785434373176</v>
+        <v>-3.385666119436521</v>
       </c>
       <c r="G85">
-        <v>-4.476884988880153</v>
+        <v>-4.822691333730264</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>0.01589962346040191</v>
       </c>
       <c r="E86">
-        <v>-21.84775172398546</v>
+        <v>-21.81609769067184</v>
       </c>
       <c r="F86">
-        <v>-2.846560471857589</v>
+        <v>-3.711363614869231</v>
       </c>
       <c r="G86">
-        <v>-4.647851492164735</v>
+        <v>-5.126255117499275</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>0.1356392100338166</v>
       </c>
       <c r="E87">
-        <v>-22.165700412538</v>
+        <v>-21.67585085065429</v>
       </c>
       <c r="F87">
-        <v>-2.971253788633596</v>
+        <v>-3.965206036680903</v>
       </c>
       <c r="G87">
-        <v>-4.022721177984157</v>
+        <v>-5.298876893553492</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>0.2147123586356455</v>
       </c>
       <c r="E88">
-        <v>-24.63257757126841</v>
+        <v>-22.88096382510152</v>
       </c>
       <c r="F88">
-        <v>-3.275963767548977</v>
+        <v>-3.644699091394135</v>
       </c>
       <c r="G88">
-        <v>-4.579882681697958</v>
+        <v>-4.221532679799548</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>0.2536001696694746</v>
       </c>
       <c r="E89">
-        <v>-25.09116254860317</v>
+        <v>-23.95077052467356</v>
       </c>
       <c r="F89">
-        <v>-3.223755911987538</v>
+        <v>-3.968446609960655</v>
       </c>
       <c r="G89">
-        <v>-4.133912471011658</v>
+        <v>-4.726947046189002</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>0.2509290753316663</v>
       </c>
       <c r="E90">
-        <v>-25.58855654818365</v>
+        <v>-26.47703862001457</v>
       </c>
       <c r="F90">
-        <v>-3.169698312015648</v>
+        <v>-4.180352103638199</v>
       </c>
       <c r="G90">
-        <v>-4.634079622721367</v>
+        <v>-4.153649943516792</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>0.208743205558563</v>
       </c>
       <c r="E91">
-        <v>-28.66200015787147</v>
+        <v>-27.0937126249571</v>
       </c>
       <c r="F91">
-        <v>-2.931684334536669</v>
+        <v>-4.409372496224984</v>
       </c>
       <c r="G91">
-        <v>-3.879977075421861</v>
+        <v>-4.531790386648965</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>0.1265600343099127</v>
       </c>
       <c r="E92">
-        <v>-29.9287524562741</v>
+        <v>-28.58958533001482</v>
       </c>
       <c r="F92">
-        <v>-3.268988914017405</v>
+        <v>-4.781749323172848</v>
       </c>
       <c r="G92">
-        <v>-4.550915408229335</v>
+        <v>-4.487604535336313</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>0.003816166193727898</v>
       </c>
       <c r="E93">
-        <v>-30.99531903269366</v>
+        <v>-30.29825555716697</v>
       </c>
       <c r="F93">
-        <v>-4.119245925435887</v>
+        <v>-4.614186336567162</v>
       </c>
       <c r="G93">
-        <v>-4.152160198024121</v>
+        <v>-4.864152606064096</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.1561741774641654</v>
       </c>
       <c r="E94">
-        <v>-33.44253355728277</v>
+        <v>-32.38608359179635</v>
       </c>
       <c r="F94">
-        <v>-4.316157969122761</v>
+        <v>-4.943942832273589</v>
       </c>
       <c r="G94">
-        <v>-4.340318364294138</v>
+        <v>-4.762727422377445</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.352614484470986</v>
       </c>
       <c r="E95">
-        <v>-35.02865648507635</v>
+        <v>-35.59851286149058</v>
       </c>
       <c r="F95">
-        <v>-4.598709948380658</v>
+        <v>-4.881700133994637</v>
       </c>
       <c r="G95">
-        <v>-3.924570123835844</v>
+        <v>-4.784302247656876</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.5854826158933552</v>
       </c>
       <c r="E96">
-        <v>-37.08180320151799</v>
+        <v>-37.08382516516241</v>
       </c>
       <c r="F96">
-        <v>-4.138857523697166</v>
+        <v>-5.206961079806071</v>
       </c>
       <c r="G96">
-        <v>-5.390241329346298</v>
+        <v>-5.627488264872629</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-0.8453895933658292</v>
       </c>
       <c r="E97">
-        <v>-40.06530226046546</v>
+        <v>-38.77112099499836</v>
       </c>
       <c r="F97">
-        <v>-4.477240637536347</v>
+        <v>-5.238572408264303</v>
       </c>
       <c r="G97">
-        <v>-5.433761761005558</v>
+        <v>-5.850638897492742</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.136996419781204</v>
       </c>
       <c r="E98">
-        <v>-43.59233820489457</v>
+        <v>-40.89244388762548</v>
       </c>
       <c r="F98">
-        <v>-5.15505143650964</v>
+        <v>-5.460964204893886</v>
       </c>
       <c r="G98">
-        <v>-5.702419152608493</v>
+        <v>-6.400126556646513</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.443848450711923</v>
       </c>
       <c r="E99">
-        <v>-44.19966091101126</v>
+        <v>-41.88038030561285</v>
       </c>
       <c r="F99">
-        <v>-5.182567316528431</v>
+        <v>-5.741619222799373</v>
       </c>
       <c r="G99">
-        <v>-5.873163849341943</v>
+        <v>-6.249576187702617</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-1.777817482417648</v>
       </c>
       <c r="E100">
-        <v>-46.48275221637737</v>
+        <v>-45.07320807556488</v>
       </c>
       <c r="F100">
-        <v>-5.216835219247441</v>
+        <v>-6.379265385696827</v>
       </c>
       <c r="G100">
-        <v>-7.018255067011533</v>
+        <v>-7.642425322985723</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-2.106486689699361</v>
       </c>
       <c r="E101">
-        <v>-48.39554567366228</v>
+        <v>-46.33000905233565</v>
       </c>
       <c r="F101">
-        <v>-4.887057185988541</v>
+        <v>-6.142951632312094</v>
       </c>
       <c r="G101">
-        <v>-6.443633746123616</v>
+        <v>-7.909639316733536</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.472460514727254</v>
       </c>
       <c r="E102">
-        <v>-49.31429380152345</v>
+        <v>-48.59809865543286</v>
       </c>
       <c r="F102">
-        <v>-5.243979990669778</v>
+        <v>-6.117061009137595</v>
       </c>
       <c r="G102">
-        <v>-6.862116497197347</v>
+        <v>-7.633132621656989</v>
       </c>
     </row>
   </sheetData>
